--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44958</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45813</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>44558</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>46104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44706</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45235</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45954</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44743</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45187</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45659</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>44949</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45624</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46260</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44483</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>45484</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45484</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45307</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45301</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45693</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44466</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>45030</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45078</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44801</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45544</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>45719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44642</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45331</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45229</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44701</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45977</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45982</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45160</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45624</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>46174</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>46043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>46043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>46174</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>46175</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>46175</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44517</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>46190</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>45307</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44851</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>46199</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45861</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>44525</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>46238</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45796</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45420</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45411</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44463</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44484</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44743</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44568</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44799</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44782</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44739</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44587</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44465</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44467</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44466</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44466</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44517</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44739</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44734</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44861</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44616</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44484</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44796</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44837</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44466</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44836</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44874</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44714</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44483</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44486</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44721</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44873</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44697</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44805</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44704</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44720</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44789</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45400</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45174</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45351</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45369</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44998</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44897</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45030</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44826</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44755</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45145</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45098</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45355</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44918</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44918</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44918</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45184</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45188</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45530</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44882</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45383</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>45141</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45475</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45020</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44852</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45049</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45665</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45315</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45351</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45635</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45098</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45148</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45062</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45078</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45219</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45551</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44851</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45201</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45187</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>45567</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44918</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44918</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45708</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45145</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45660</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>44958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45456</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>44732</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44935</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44677</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45560</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45358</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44483</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45601</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45369</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45360</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44799</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45629</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45468</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45245</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>45007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44502</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45334</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45267</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45321</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45020</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45383</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44981</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44627</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>44949</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44725</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45187</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45352</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45461</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44960</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45442</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45302</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45882</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44799</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45107</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45145</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44860</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45676</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45008</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45943</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45184</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44882</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45390</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45929</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45250</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45385</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45888</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45671</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45971</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45933</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45527</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45567</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45904</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45590</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45461</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45823</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44728</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45035</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44623</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>44484</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45818</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45777</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45597</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45562</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>46140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45456</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45334</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45912</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44480</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45917</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44991</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>44617</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45361</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44650</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45593</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45267</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45929</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44977</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45111</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45062</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45118</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44918</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45245</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45940</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45315</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>46148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45631</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45929</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45946</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>46147</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45693</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45593</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44739</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44959</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45118</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46153</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44952</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45684</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46153</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45967</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>44952</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>44483</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45613</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45176</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45118</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45161</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45161</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45161</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45385</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>44616</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45139</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45235</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45708</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45708</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>44483</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45988</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45988</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45988</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45315</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45145</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45994</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45770</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45989</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45082</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46002</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45327</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>46002</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46003</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>46002</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>44805</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>46008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>44868</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45202</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45007</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44462</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45560</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>46170</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45393</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45588</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45086</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45260</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45219</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>46034</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45348</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46036</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>44882</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>44657</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44599</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45314</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45576</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45349</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44721</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>46045</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46176</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44953</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45576</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46175</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45348</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45351</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44575</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45188</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46176</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46175</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45308</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46176</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46176</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>46176</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46175</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45120</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46177</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46176</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46175</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46052</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>46178</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45448</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45267</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45360</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45360</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45078</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>46178</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45539</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46177</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>44978</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45686</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45761</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45400</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>46181</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>46181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45770</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>46077</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45531</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46080</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>46080</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>44539</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45195</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>46085</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44677</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44799</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45360</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46090</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45485</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45198</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46176</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>46094</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45674</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45929</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45098</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45240</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45379</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45226</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44965</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>44851</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46105</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45483</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>46197</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45595</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44645</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45324</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46197</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45160</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46202</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>46199</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>46120</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45531</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45001</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44982</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45123</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45398</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45607</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45082</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44795</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>46002</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45695</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45539</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45048</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45821</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45476</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45476</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45030</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45517</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46203</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45071</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>46206</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46206</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45470</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44594</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45333</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46206</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>44956</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>46206</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>46206</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>46205</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45078</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45042</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>46252</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>44811</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45540</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45260</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45476</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45229</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45341</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44594</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>46211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45187</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45439</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46211</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45175</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45014</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45399</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45260</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45294</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46206</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45709</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>46206</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>44974</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45737</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>44868</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>44658</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45442</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45134</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45097</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45475</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>44907</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45646</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45071</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>46226</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45785</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46279</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46279</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45755</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46279</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45632</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>44988</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45361</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45755</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45526</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45791</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>46240</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45799</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44918</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45817</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45832</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45821</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>45601</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45841</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45841</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45624</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45733</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45825</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45786</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45866</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45796</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44413</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45513</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>44847</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45378</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45393</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45705</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>45875</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46083</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>46085</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46126</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45813</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45208</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44558</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44706</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45235</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45954</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44743</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45957</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45635</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45659</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45624</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44949</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44466</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45832</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46043</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44918</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44914</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44701</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45982</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>45861</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45898</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>46002</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46002</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45030</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45030</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45965</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45331</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>46175</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>46175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46174</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>46174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>44636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46190</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>46199</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45160</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44608</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46206</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45196</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>45307</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>46238</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44525</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44801</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45420</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44805</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44852</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44776</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44484</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44483</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44568</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44729</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44782</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44739</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44587</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44465</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44467</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44466</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44739</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44734</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44852</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44861</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>44616</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44484</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44837</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44466</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44836</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44874</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44714</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44483</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44486</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44560</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44721</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44873</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44697</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44704</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44603</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44720</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44789</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44799</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44799</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44811</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45360</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45360</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44725</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45379</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45385</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45461</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>45315</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45360</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45442</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>44958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>45314</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45468</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45259</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45576</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44868</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45294</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45485</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45476</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45120</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45888</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45475</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45327</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45082</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45593</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45456</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>44918</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44918</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45539</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44650</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46052</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45476</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45358</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45527</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45912</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45007</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45390</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45355</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45014</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45098</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45139</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45369</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45567</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45929</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45145</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44657</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46080</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45576</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45442</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46085</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45560</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45613</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45229</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45588</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45940</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46094</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45141</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44918</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45235</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45540</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45946</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46105</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44677</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45062</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>44960</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46120</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45360</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45361</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44599</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45593</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45967</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45334</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45590</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44502</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45973</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44483</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45695</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45943</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45818</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44739</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45078</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45933</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45988</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45882</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45597</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45817</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45866</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45994</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45989</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45184</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44981</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45020</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45909</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>46140</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46002</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45777</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>44882</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>46002</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46002</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45530</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45078</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>46003</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45823</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46007</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45901</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45665</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46002</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45671</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45929</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44882</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44935</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44617</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45042</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45821</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45708</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44907</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45082</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>46148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45148</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45400</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45737</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>46147</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>46153</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45757</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45315</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45821</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45078</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45601</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44483</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44959</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45048</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45733</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45825</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45624</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45086</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46168</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45393</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45770</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45341</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45145</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46175</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46175</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45786</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46175</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45560</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46177</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44575</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45866</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45475</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46175</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45348</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>46176</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45531</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46176</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46178</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46178</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45267</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45250</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45020</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45302</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45123</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45383</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45533</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45470</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45333</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45351</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45929</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45601</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45188</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45000</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>46197</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45071</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46199</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45049</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45187</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>45796</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46203</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46202</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45595</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46205</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45078</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45684</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44795</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46206</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46206</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45385</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>44608</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46206</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46206</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45324</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45062</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>46206</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44623</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45383</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45351</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>44658</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44728</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44677</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45260</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45709</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45184</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45149</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45245</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46206</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44799</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46206</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45693</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44882</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45245</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44799</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44852</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45398</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44805</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45399</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>46226</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45531</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45352</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45351</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45294</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46272</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44949</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45301</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45219</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45761</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44851</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>46279</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>46279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44627</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>46279</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44480</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45118</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45308</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45461</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>46286</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>46240</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>46286</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45348</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>44953</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>46288</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45456</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44594</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45187</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45098</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>44967</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44645</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>46287</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45118</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>45062</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45541</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>44860</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45187</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45476</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46289</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>45267</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>44960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45439</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45245</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44918</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45260</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45118</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44616</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45267</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45145</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>44483</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45369</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45567</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45686</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>44998</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45607</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45145</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>44539</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44970</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45188</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>44484</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45349</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45676</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45035</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44897</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45266</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45071</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45400</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>44982</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>44732</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45315</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45226</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45321</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45562</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44755</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45539</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44977</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45551</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44952</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45201</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45708</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45708</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45517</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44956</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45240</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44952</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>44918</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45008</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45631</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45111</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45660</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45770</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45361</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44988</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45755</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45755</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45632</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45785</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45526</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45791</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>44413</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45513</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>44847</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45378</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45393</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45705</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>45875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46083</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46085</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>46126</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>45813</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45208</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44558</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44706</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45235</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45954</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44743</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45957</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45635</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45659</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45624</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44949</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44483</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44466</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45832</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46043</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44918</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44914</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44701</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45982</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>45861</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45898</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>46002</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46002</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>45030</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45030</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45965</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45331</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>46175</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>46175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46174</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>46174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>44636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46190</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>46199</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45160</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44608</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46206</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45196</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>45307</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>46238</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44851</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44525</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44801</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45420</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45411</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44805</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44852</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44776</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44481</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44484</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44483</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>44568</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44729</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44782</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44739</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44587</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44465</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44467</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44466</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44739</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44734</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44852</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44861</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>44616</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44484</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44837</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44466</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44836</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44874</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44714</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44483</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44486</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44560</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44721</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44873</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44697</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44704</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44603</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44720</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44789</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44799</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44799</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44811</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45360</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45360</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44725</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45379</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45385</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45461</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>45315</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45360</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45442</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>44958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>45314</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45468</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45259</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45576</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44868</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45294</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45485</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45476</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45120</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>46034</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45888</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45475</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45195</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45327</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45082</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45593</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45456</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>44918</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44918</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45539</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44650</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46052</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45476</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45358</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45527</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45912</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45007</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45390</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45355</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45014</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45098</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45139</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45369</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45567</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45929</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45145</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44657</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46080</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45576</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45442</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46085</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45560</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45613</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45229</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45588</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45940</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46094</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45141</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44918</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45235</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45540</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45946</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46105</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44677</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45062</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>44960</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>46120</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45360</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45361</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44599</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45593</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45967</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45334</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45590</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44502</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45973</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44483</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45646</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45695</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45943</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45818</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44739</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45078</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45933</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45988</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45882</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45597</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45817</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45866</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45994</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45989</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45184</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44981</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45020</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45909</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>46140</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46002</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45777</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>44882</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>46002</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46002</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45530</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45078</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>46003</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45823</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46007</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45901</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45665</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46002</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45671</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45929</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44882</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44935</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44617</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45042</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45821</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45708</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44907</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45082</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>46148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45148</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45400</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45737</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>46147</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>46153</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45757</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45315</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45821</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45078</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45601</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44483</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44959</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45048</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45733</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45825</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45624</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45086</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46168</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45393</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45770</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45341</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>45145</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46175</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46175</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45786</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46175</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>46177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45560</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46177</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44575</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46176</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45866</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45475</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46175</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45348</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>46176</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45531</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46176</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46178</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46178</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45267</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45250</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45020</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45302</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45123</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45383</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45533</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45470</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45333</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45351</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45929</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45601</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45188</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45000</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>46197</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45071</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46199</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45049</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45187</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>45796</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46203</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46202</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45595</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46205</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45078</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45160</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45684</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44795</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46206</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46206</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45385</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>44608</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46206</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46206</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45324</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45062</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>46206</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44623</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45383</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45351</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>44658</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44728</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44677</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45260</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45709</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45184</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45149</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45245</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46206</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44799</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46206</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45693</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44882</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45245</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44799</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44852</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45398</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44805</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45399</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>46226</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45531</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45352</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45351</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45294</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46272</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44949</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45301</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45219</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45761</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44851</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>46279</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>46279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44627</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>46279</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44480</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45118</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45308</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45461</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>46286</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>46240</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>46286</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45348</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>44953</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>46288</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45456</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44594</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45187</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45098</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>44967</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44645</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>46287</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45118</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>45062</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45541</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>44860</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45187</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45476</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46289</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>45267</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>44960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45439</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>45245</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44918</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45260</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45118</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44616</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45267</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45145</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>44483</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45369</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45567</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45686</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>44998</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45607</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45145</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>44539</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44970</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45188</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>44484</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45349</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45676</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45035</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44897</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45266</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45071</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45400</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>44982</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>44732</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45315</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45226</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45321</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45562</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44755</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45539</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44977</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45551</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>44952</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45201</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45708</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45708</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45517</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44956</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45240</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44952</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>44918</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45008</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45631</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45111</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45660</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45770</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45361</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44988</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45755</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45755</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45632</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45785</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45526</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45791</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>44413</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45513</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>44847</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45378</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45393</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45705</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>45875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46083</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46085</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>46126</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44958</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45813</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45096</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>44558</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44706</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>45954</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45235</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>44743</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45187</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44949</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45624</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44687</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44873</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45307</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45301</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45030</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44801</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>45544</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44918</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46043</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>45719</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45977</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45331</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45861</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45898</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44914</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>46174</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45160</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46175</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>46175</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>46190</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>46199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>46206</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44517</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46244</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45307</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44851</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>46294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44525</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44886</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45420</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45411</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>44776</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44743</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44568</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44587</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44729</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44782</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44739</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44734</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44852</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44861</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44616</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44484</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44796</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44837</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44836</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44714</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44483</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44486</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44560</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44721</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44873</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44697</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44704</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44603</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44720</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45369</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44789</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44998</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44852</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45174</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45351</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44826</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44755</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45030</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44918</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44918</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45145</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45184</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45098</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45188</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45383</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45632</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45475</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45361</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45148</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45665</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45315</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46002</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>46007</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45351</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>46008</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45098</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45635</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45533</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45888</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44851</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>46034</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45187</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45567</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>44918</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45912</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45660</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45145</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>44918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>44958</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45259</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45456</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44935</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44732</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44677</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45560</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45940</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45358</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45757</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>46080</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45369</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44483</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45062</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45360</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45601</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45517</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45957</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45629</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46090</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44502</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45245</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45817</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46094</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45020</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45967</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45334</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45321</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>44981</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45167</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45383</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>44627</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>46105</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44725</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45187</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45461</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45442</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45302</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44960</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45988</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45245</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46120</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44799</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45994</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45145</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>44860</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45676</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45294</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45989</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45008</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44882</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45390</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45250</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45385</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45671</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45832</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45527</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45567</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45821</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>46002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45590</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45695</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45821</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45461</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45841</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44728</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45841</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45035</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44623</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45901</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45624</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45882</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45733</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45825</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45562</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45456</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45334</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45943</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45929</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44480</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45971</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44991</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44617</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45933</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45361</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44650</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45593</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45888</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45777</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45789</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45597</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45111</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45062</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45909</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46140</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45118</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45786</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45572</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45866</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45245</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45315</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45160</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45593</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44739</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45078</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44959</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45118</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44608</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45684</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44483</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45613</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45176</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45118</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45161</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45385</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44616</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45139</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45235</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45301</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45708</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45708</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44483</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>46174</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45796</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46176</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46176</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46175</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46176</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46176</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46176</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46175</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>46176</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>46175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>46178</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45315</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>46178</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46177</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45145</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45770</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45082</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45327</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>46176</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44805</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45929</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44868</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>46197</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45007</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45560</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>46202</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45393</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45588</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45086</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>44960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45260</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>46203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45219</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45348</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46206</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>46206</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46206</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46206</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44882</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>46206</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44657</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>44599</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45314</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46211</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45576</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45349</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>44721</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44953</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45576</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45348</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45351</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>44575</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45308</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45120</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46206</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45448</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45360</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45360</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45078</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45539</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44978</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45686</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45761</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45400</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45154</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46226</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46272</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45770</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45531</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46272</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44970</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44539</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45195</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>46279</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46279</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46279</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44677</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45360</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45485</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>44964</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>46240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45240</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45379</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45226</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44965</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44851</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46286</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45483</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45595</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44645</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45324</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>46289</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46287</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45531</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44982</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45123</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45398</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45607</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>46295</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45082</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45539</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>45476</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46294</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46294</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>46252</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45476</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46295</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45030</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45517</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45071</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45470</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44594</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45333</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44956</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45078</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45042</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>44811</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45540</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45476</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45341</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44594</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45187</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45439</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45175</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45014</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45399</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45260</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45709</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44974</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45737</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44868</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>44658</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45442</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45097</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45475</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44907</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45646</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45071</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45785</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45755</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>44413</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45513</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>44847</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45378</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45393</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45705</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45875</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46083</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46085</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46126</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44958</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45813</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45096</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>44558</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44706</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>45954</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45235</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>44743</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45187</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44949</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45624</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44687</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44873</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44483</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45307</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45301</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45030</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44801</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>45544</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44918</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46043</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>45719</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45977</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45331</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45861</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45898</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>44914</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>46174</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45160</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46175</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>46175</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>46190</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>46199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>46206</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44517</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46244</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45307</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44851</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>46294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44525</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44886</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45420</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45411</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>44776</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44743</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44568</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44587</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44729</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44782</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44739</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44734</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44852</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44861</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44616</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44484</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44796</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44837</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44836</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44714</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44483</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44486</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44560</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44721</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44873</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44697</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44704</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44603</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44720</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45369</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44789</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45530</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44998</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44852</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45174</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45351</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44826</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44755</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45030</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44918</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44918</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45145</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45184</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45098</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45188</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45383</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44930</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45632</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45475</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45361</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45148</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45665</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45315</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46002</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>46007</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45351</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>46008</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45098</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45635</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45533</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45888</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44851</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>46034</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45187</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45567</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>44918</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45912</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45660</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45145</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>44918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>44958</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45259</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45456</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44935</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44732</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44677</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45560</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45940</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45358</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45757</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45946</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>46080</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45369</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44483</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45062</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45360</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45601</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45517</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45957</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45629</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46090</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44502</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45245</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45817</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46094</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45020</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45967</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45334</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45321</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>44981</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45167</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45383</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>44627</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>46105</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44725</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45187</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45461</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45442</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45302</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44960</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45988</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45245</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46120</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44799</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45994</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45145</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>44860</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45676</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45294</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45989</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45008</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44882</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45390</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45250</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45385</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45671</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45832</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45527</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45567</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45821</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>46002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45590</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45695</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45821</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45461</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45841</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44728</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45841</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45035</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44623</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45901</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45624</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45882</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45733</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45825</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45562</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45456</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45334</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45943</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45929</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44480</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45971</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44991</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44617</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45933</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45361</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44650</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45593</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45888</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45777</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45789</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45597</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45111</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45062</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45909</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46140</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45118</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45786</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45572</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45866</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45245</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45315</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45160</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45593</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44739</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45078</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44959</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45118</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44608</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45684</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44483</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45613</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45176</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45118</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45161</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45385</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44616</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45139</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45235</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45301</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45708</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45708</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44483</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>46174</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45796</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46176</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46176</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46175</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46176</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46176</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46176</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46175</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>46176</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>46175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>46178</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45315</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>46178</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46177</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45145</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45770</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45082</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45327</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>46176</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44805</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45929</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44868</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>46197</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45007</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45560</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>46202</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45393</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45588</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45086</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>44960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45260</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>46203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45219</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45348</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46206</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>46206</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46206</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46206</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44882</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>46206</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44657</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>44599</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45314</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46211</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45576</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45349</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>44721</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44953</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45576</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45348</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45351</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>44575</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45308</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45120</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46206</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45448</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45360</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45360</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45078</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45539</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44978</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45686</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45761</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45400</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45154</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46226</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46272</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45770</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45531</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46272</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44970</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44539</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45195</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>46279</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46279</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46279</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44677</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44799</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45360</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45485</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>44964</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>46240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45240</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45379</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45226</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44965</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44851</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46286</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45483</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45595</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44645</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>46286</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45324</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>46289</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46287</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45531</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44982</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45123</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45398</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45607</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>46295</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45082</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45539</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>45476</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46294</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46294</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>46252</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45476</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46295</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45030</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45517</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45071</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45470</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44594</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45333</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44956</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45078</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45042</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>44811</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45540</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45476</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45341</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44594</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45187</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45439</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45175</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45014</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45399</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45260</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45709</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44974</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45737</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44868</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>44658</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45442</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45097</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45475</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44907</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45646</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45071</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45785</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45755</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>44413</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45513</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>44847</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45378</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45393</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45705</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45875</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46083</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46085</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46126</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>46139</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44958</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44939</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46294</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45096</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45208</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>44558</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>46104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44706</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45235</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>44743</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45624</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>44949</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>46260</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>44687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>44873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44483</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45307</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45484</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45693</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45680</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>46031</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>46274</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44754</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>44497</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44642</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>44886</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45331</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44914</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45160</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44608</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45307</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45030</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45030</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45719</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44851</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44525</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44801</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>46002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45861</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45229</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45965</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>46175</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>46175</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>46174</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46174</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46190</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>46199</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46238</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>46244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>46294</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>46295</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>46301</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44484</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44743</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44568</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44782</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44739</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44587</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44483</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44836</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44517</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44616</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44484</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44486</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44560</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44739</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44721</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44697</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44837</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44734</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44874</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44805</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>44714</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44704</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44852</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44603</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44720</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45145</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44539</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>44789</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45082</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45379</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45148</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44991</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45483</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45400</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45737</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>44799</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44799</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45160</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45315</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45385</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44484</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45334</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45349</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45676</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45035</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44897</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45360</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45360</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45049</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>44725</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45461</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44483</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45048</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45315</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44868</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45266</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45071</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45442</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45360</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>44958</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45400</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44982</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45259</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45001</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44732</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45314</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45468</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45315</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45219</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45226</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45393</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45321</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45770</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45576</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45562</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44755</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45539</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44977</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45551</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44952</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45201</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45708</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45517</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44956</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44868</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45341</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45294</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45145</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45888</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45240</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45485</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>44952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45476</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45162</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44918</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45120</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45161</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45161</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45475</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45660</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45770</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45560</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45327</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45348</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45531</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45082</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45267</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45593</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45448</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45912</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45250</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45456</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44918</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45302</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44650</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45476</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45361</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45358</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44988</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44952</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45527</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45517</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45007</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45123</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45383</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45755</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>45533</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45390</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45470</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45260</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45755</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45632</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45785</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45355</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45333</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45351</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45526</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45014</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45791</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45601</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45098</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45139</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45188</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45369</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45000</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45929</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45567</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45145</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45071</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44657</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45576</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45442</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45049</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45635</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45187</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44594</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45560</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44974</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44964</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45613</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45229</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45595</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45799</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45588</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45141</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45160</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44918</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45684</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45235</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44918</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44795</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45540</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45385</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44608</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45324</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45062</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45940</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>44677</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45062</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45946</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>44623</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45383</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45351</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44658</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45167</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44721</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45817</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45929</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44728</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>44960</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44677</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45360</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45361</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44599</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45593</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45260</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45709</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45184</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44918</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45149</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45334</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45245</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45832</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45590</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45957</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45198</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44502</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>45821</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45078</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45601</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>44799</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>44483</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45693</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45202</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45646</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45174</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45967</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>44739</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45134</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45841</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45078</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44882</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45733</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45825</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45624</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45154</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45245</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44799</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45629</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44852</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45398</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45184</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44981</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45020</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44805</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45399</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45531</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45786</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45352</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44882</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45351</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45866</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45530</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44949</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45030</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45078</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>45301</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45665</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45219</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45761</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44826</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44851</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45671</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44882</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44935</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44617</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45042</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44952</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45796</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45176</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45098</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44851</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44627</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45175</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44930</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>44480</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>46105</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>45708</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45118</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45308</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44907</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45988</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45461</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45988</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45988</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45082</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45994</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45348</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46120</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44953</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45989</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>46002</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45456</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>44594</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>46002</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>45187</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45098</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46002</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44967</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>44645</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45695</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45118</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>46003</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45062</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45943</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45818</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45541</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45933</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44860</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>46007</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46008</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45187</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45882</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45597</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45866</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45476</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45267</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>44960</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45909</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46140</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45439</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45777</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45245</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44918</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45260</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46034</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45118</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45823</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44616</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45901</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>46002</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45267</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45929</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45145</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45097</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45821</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>44483</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45789</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45030</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45888</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45369</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45909</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46045</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45567</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45686</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45971</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44998</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45607</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46052</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46148</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46147</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46153</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46153</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46080</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>46085</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>46090</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>46168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46170</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46175</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>46175</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>46176</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>46176</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>46176</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>46176</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>46176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46175</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>46176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>46178</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46181</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45929</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>46197</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46203</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>46202</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46205</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>46206</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>46206</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46206</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>46206</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46211</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>46206</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>46206</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46226</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46272</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>46272</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46279</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>46279</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46279</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46279</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46286</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46240</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46286</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46288</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>46287</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>46036</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46289</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>46252</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>46294</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>46295</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>46295</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46299</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>46299</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>46298</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>46300</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46302</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>46302</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46304</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>46302</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>44413</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45513</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>44847</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45378</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45393</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45705</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45875</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>46083</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>46085</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>46126</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44706</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45208</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45813</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45096</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44558</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>46104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45235</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45954</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44949</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45624</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>46260</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45484</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45484</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45307</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45301</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45693</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44801</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44642</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45331</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45965</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44701</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44914</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>46174</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45160</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>46174</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45624</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>46175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46175</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46190</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>46199</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45861</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46206</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45307</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44851</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44525</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>46294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>46307</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44729</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44739</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44517</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44739</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44861</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44837</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44839</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44733</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44714</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44486</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44560</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44721</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44873</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44704</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44720</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>44789</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45400</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45078</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45530</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44852</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45351</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45369</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44998</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44826</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45030</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44755</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45355</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45145</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44918</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44918</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44918</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44882</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45383</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45475</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45141</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45148</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45315</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45351</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45635</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45049</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44851</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45665</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45201</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45567</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45149</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45708</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44918</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45660</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45145</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44732</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44677</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44935</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45358</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45601</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45757</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45062</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45360</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45517</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44799</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45468</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45245</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44502</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45321</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45020</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45383</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>44627</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44725</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44949</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45352</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45187</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45442</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45461</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45909</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45882</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45866</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45302</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>44960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45943</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45245</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45933</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45145</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45888</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45823</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45676</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45294</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45008</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45184</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45888</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45818</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45390</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45250</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45385</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45777</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45789</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45597</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45671</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45909</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45527</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45567</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45590</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45461</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44728</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45912</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44623</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45917</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45562</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45456</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45334</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45929</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44991</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44617</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45361</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44650</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45593</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45267</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45940</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44977</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45062</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45929</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46153</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45957</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45118</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44918</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44952</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45315</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45967</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45973</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45541</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45693</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45160</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45593</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44739</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44952</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44952</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45988</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45613</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45988</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45118</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45161</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45161</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45385</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45139</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45235</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44952</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46170</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45989</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45708</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46002</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46002</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46002</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>46007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46008</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46174</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45315</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>46176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45145</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46175</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45770</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>46175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46176</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>46178</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>45082</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>46178</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45327</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>46177</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46045</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>44805</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44868</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>46052</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45202</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45560</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45393</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45588</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45086</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>46080</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45348</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46085</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44882</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46176</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>44657</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46090</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44599</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>45314</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45576</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45929</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45349</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44721</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44953</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45576</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45348</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45351</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44575</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45188</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45308</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45120</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45448</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45267</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46197</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45360</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45360</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45078</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45539</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46202</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45686</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45761</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46120</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45400</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45531</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44539</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46203</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44677</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44799</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45360</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45695</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45485</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45821</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46206</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>46205</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46206</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45098</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45240</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45379</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45226</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44965</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46211</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44851</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45595</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>44645</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45324</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46206</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45160</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46226</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>46272</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46272</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45531</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45001</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44982</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45123</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45398</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46279</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46279</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45607</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45000</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45082</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>44795</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45539</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45048</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45476</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45476</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45030</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45071</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45470</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44594</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45333</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44956</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46286</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45078</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45042</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>46286</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>44811</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45540</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45476</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45229</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45341</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>44594</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>46289</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45187</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45439</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45014</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45082</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45399</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46287</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45294</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>46036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45709</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>46295</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>44974</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45737</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46294</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46252</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>46295</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>44868</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>46294</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44658</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45442</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>45134</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45097</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45475</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>44907</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45646</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45071</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46300</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46298</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45785</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46299</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46299</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45755</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46302</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45632</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44988</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45361</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45755</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45526</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>46302</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45791</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46302</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>46307</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>46307</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46304</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45799</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>46307</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44918</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45817</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46310</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45832</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45821</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45601</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45841</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45841</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45733</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45825</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45786</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45866</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45796</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44413</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45513</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>44847</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45378</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45393</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45705</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45875</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>46083</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46085</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>46126</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44706</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45208</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45813</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45096</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44558</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>46104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45235</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45954</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45659</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44949</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45624</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>46260</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45484</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45484</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45307</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45301</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45693</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44801</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44642</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45331</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45965</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44701</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44914</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>46174</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45160</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>46174</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45624</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>46175</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46175</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46190</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>46199</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44517</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45861</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46206</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45307</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44851</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>46238</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44525</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>46002</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>46294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>46307</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44729</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44739</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44517</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44739</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44861</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44837</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44839</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44733</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44714</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44486</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44560</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44721</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44873</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44704</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44720</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>44789</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45400</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45078</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45530</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44852</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45351</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45369</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44998</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44826</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45030</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44755</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45355</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45145</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44918</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44918</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44918</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44882</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45383</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45475</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45141</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45148</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45315</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45351</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45635</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45049</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44851</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45665</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45201</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45567</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45149</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45708</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44918</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45660</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45145</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44732</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44677</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44935</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45358</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45601</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45757</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45062</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45360</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45517</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44799</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45468</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45245</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44502</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45321</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45020</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45383</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>44627</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44725</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44949</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45352</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45187</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45442</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45461</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45909</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45882</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45866</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45302</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>44960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45943</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45245</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45929</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45933</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45145</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45888</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45823</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45676</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45294</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45008</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45184</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45888</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45818</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45390</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45250</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45385</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45777</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45789</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45597</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45671</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45909</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45527</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45567</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45590</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45461</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44728</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45912</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44623</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45917</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45562</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45456</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45334</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45929</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44991</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44617</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45361</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44650</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45593</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45267</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45940</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44977</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45062</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45929</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46153</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45957</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45118</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44918</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44952</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45315</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45967</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45973</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45541</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45693</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45160</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45593</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44739</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44952</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44952</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45988</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45613</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45988</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45118</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45161</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45161</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45385</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45139</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45235</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44952</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46170</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45989</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45708</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46002</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46002</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46002</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>46007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46008</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46174</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45315</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>46176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45145</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46175</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45770</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>46175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46176</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>46178</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>45082</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>46178</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45327</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>46177</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46045</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>44805</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44868</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>46052</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45202</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45560</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45393</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45588</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45086</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>46080</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45348</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46085</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44882</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46176</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>44657</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46090</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44599</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>45314</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45576</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45929</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45349</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44721</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44953</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45576</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45348</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45351</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44575</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45188</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45308</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45120</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46105</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45448</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45267</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46197</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45360</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45360</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45078</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45539</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46202</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>46199</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45686</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45761</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>46120</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45400</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45531</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44539</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46203</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44677</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44799</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45360</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45695</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45485</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45821</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46206</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46206</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>46205</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46206</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45098</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45240</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45379</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45226</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44965</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46211</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44851</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45595</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>44645</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45324</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46206</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45160</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46226</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>46272</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46272</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45531</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45001</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44982</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45123</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45398</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46279</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46279</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45607</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45000</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46279</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45082</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>44795</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45539</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45048</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45476</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45476</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45030</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45071</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45470</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44594</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45333</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44956</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46286</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45078</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45042</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>46286</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>44811</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45540</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45476</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45229</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45341</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>44594</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>46289</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45187</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45439</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45014</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45082</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45399</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46287</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45294</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>46036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45709</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>46295</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>44974</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45737</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46294</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46252</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>46295</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>44868</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>46294</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44658</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45442</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>45134</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45097</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45475</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>44907</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45646</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45071</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46300</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46298</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45785</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46299</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46299</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45755</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46302</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45632</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44988</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45361</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45755</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45526</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>46302</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45791</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46302</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>46307</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>46307</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46304</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45799</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>46307</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44918</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45817</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46310</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45832</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45821</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45601</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45841</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45841</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45733</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45825</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45786</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45866</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45796</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44413</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45513</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>44847</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45378</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45393</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45705</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45875</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>46083</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46085</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>46126</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44706</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>46294</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44558</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45096</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45954</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45235</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>46260</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45624</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44949</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45307</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45301</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45832</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>46175</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46175</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>46174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>46174</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45982</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>46206</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45544</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46238</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>46244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>46002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>46294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>46295</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44914</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46307</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45898</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45229</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44701</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>45624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45030</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44517</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45331</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45078</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44608</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45307</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44801</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44729</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44739</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44517</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44739</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44861</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44837</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44839</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44733</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44714</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44560</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44721</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44697</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44704</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44805</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44603</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44789</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45118</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45062</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44991</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44799</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44799</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45541</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45334</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44811</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45360</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45360</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44725</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45187</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45476</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45267</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45439</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45245</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45912</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44918</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45260</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45118</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45917</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44616</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46168</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45145</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45379</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45030</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45369</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46170</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45567</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46175</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45686</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44839</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44998</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45607</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>46175</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44539</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45940</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44970</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45385</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46176</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45082</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46176</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46176</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46175</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46176</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45461</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45188</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45315</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45442</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45360</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44958</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46178</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45929</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46181</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45349</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45676</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45035</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45049</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45314</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45468</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45266</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>46176</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45400</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>44982</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>44732</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45219</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45315</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45321</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46197</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45973</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45539</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>46199</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45551</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45201</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45708</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45708</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44956</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>46203</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45240</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44952</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>44918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46206</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46206</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45988</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46206</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>46206</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>46206</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45988</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46206</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45660</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45576</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45770</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46206</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>46206</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46002</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>46002</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46002</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46226</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46003</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45361</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46007</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46279</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46279</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46279</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45755</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45755</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45632</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45785</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44868</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45526</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>46240</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45791</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45572</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46288</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46045</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45799</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44918</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>46036</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>46294</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46252</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46295</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46295</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46080</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45832</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45821</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45601</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46299</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46299</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46090</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45485</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46094</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45476</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45841</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46298</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45825</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45624</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45161</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45161</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45161</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>46105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46300</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46302</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45475</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45786</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>46304</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>46120</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>46302</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45195</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45327</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45796</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45082</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45695</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45593</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45448</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45456</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44918</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44918</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45943</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45539</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46307</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45818</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44650</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45933</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46307</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46307</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45476</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45882</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46310</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45358</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44952</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45527</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45597</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45517</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45007</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45390</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45866</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45909</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46140</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45355</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45866</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45823</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45014</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45901</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46002</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45929</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45821</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45139</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45789</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45567</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45888</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45909</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>46316</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45145</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44657</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46316</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46272</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45576</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45971</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45442</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>46318</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44594</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45560</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45613</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45229</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45588</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>46294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46318</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46318</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46318</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45141</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44918</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45235</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45540</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45007</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46153</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>44677</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45062</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44960</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45360</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45361</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44599</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>44918</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45334</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45590</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44502</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45078</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45646</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44739</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45078</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45154</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45629</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45184</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44981</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45020</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44882</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45530</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45030</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45078</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45665</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>44826</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>45671</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44882</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44935</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>44617</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45042</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>44952</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>44851</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>44930</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45708</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44907</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45082</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45400</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45737</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45757</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45315</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45078</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>44959</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45048</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45001</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45086</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45393</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45770</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45341</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45145</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45560</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44575</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45475</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45348</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45531</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45250</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45020</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45302</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45123</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38964,7 +38964,7 @@
         <v>45383</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45533</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45470</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45333</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45351</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45601</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45188</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45000</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45071</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45635</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>45187</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45595</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45078</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45160</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45684</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45385</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>44608</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45324</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45062</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44623</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45383</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45351</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44658</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>44721</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44728</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44677</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45260</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45709</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45184</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45149</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45245</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45198</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>44799</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45693</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45174</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45134</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44882</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45245</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44799</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45398</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44805</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45399</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45531</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45352</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45351</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45294</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>44949</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45219</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45761</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44851</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45098</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44627</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45175</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45118</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45308</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45461</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45348</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>44953</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45456</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>44594</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45187</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45098</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>44967</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44978</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>44645</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44413</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45513</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44847</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45378</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45393</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45705</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45875</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>46083</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>46085</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46126</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>46206</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45211</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44706</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44958</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>46294</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>44558</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45096</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45954</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45235</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>44743</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>46260</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45659</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45624</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44949</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44873</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45307</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45680</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45301</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46031</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44754</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45832</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>46175</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46175</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>46174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>46174</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45982</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>46206</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45544</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46238</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>46244</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>46002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>46294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>46295</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45861</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44914</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46307</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45898</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45229</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44701</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>45624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45030</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44517</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45331</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45078</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44608</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45307</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44801</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45411</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44805</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44729</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44739</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44517</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44739</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44861</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44837</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44839</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44733</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44714</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44560</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44721</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44697</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44704</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44805</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44603</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44789</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45118</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45062</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44991</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44799</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44799</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45541</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45334</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44811</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45360</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45360</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44725</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45187</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45476</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45267</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45439</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45245</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45912</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44918</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45260</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45118</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45917</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44616</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46168</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45145</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45379</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45030</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45369</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>46170</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45567</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46175</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45686</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44839</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44998</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45607</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>46175</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44539</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45940</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44970</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45385</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46176</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45082</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46176</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46176</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46175</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46176</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46176</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45461</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45188</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45315</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45442</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45360</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44958</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46178</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45929</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46181</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45349</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45676</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45035</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45049</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45314</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45468</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45266</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>46176</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45400</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>44982</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>44732</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45219</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45315</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45321</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46197</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45973</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44755</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45539</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>46199</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45551</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45201</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45708</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45708</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44956</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>46203</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45240</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44952</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>44918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45008</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46206</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46206</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45988</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46206</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>46206</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>46206</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45988</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46206</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45660</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45576</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45770</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46206</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>46206</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46002</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>46002</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46002</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46226</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46003</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45361</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46007</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46279</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46279</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46279</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45755</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45755</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45632</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45785</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44868</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45526</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>46240</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45791</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45572</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46288</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46045</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45799</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44918</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>46036</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>46294</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46252</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46295</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46295</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46080</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45832</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45821</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45601</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46299</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46299</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46090</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45485</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46094</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45476</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45841</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46298</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45825</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45624</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45161</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45161</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45161</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>46105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46300</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46302</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45475</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45786</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>46304</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>46120</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>46302</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45195</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45327</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45796</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45082</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45695</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45593</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45448</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45456</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44918</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44918</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45943</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45539</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46307</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45818</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44650</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45933</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46307</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46307</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45476</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45882</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46310</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45358</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44952</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45527</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45597</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45517</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45007</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45390</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45866</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>45260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45909</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46140</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45355</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45866</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45823</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45014</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45901</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46002</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45929</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45821</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45139</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45789</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45567</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45888</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45909</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>46316</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45145</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44657</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46316</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46316</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46272</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45576</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45971</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45442</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>46318</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44594</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45560</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45613</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45229</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45588</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>46294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>46318</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46318</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46318</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46148</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45141</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44918</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45235</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45540</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45007</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46153</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>44677</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45062</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44960</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45360</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45361</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44599</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>44918</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45334</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45590</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44502</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45078</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45646</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44739</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45078</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45154</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45629</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45184</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44981</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45020</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44882</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45530</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45030</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45078</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45665</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>44826</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>45671</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44882</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44935</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>44617</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45042</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>44952</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36754,7 +36754,7 @@
         <v>44851</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>44930</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45708</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44907</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45082</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45400</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45737</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45757</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45315</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45078</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>44959</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45048</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45001</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>44965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45086</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45393</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>45770</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45341</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45145</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45560</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44575</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45475</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45348</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45531</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45250</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45020</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45302</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45123</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38964,7 +38964,7 @@
         <v>45383</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45533</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45470</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45333</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45351</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45601</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45188</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45000</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45071</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45635</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>45187</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45595</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45078</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45160</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45684</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45385</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>44608</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45324</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45062</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44623</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45383</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45351</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44658</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>44721</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44728</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44677</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45260</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45709</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45184</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45149</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45245</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45198</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>44799</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45693</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45174</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45134</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44882</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45245</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44799</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45398</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44805</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45399</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45531</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45352</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45351</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45294</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>44949</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45219</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45761</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44851</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45098</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44627</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45175</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45118</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45308</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45461</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45348</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>44953</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45456</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>44594</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45187</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45098</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>44967</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44978</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>44645</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44413</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45513</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44847</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45378</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45393</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45705</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45875</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>46083</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>46085</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46126</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
